--- a/data/trans_bre/IP11-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 6,27</t>
+          <t>-3,51; 6,29</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-11,08; 1,7</t>
+          <t>-10,98; 0,77</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 8,23</t>
+          <t>-2,12; 7,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 4,83</t>
+          <t>-2,97; 4,75</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-53,55; 329,74</t>
+          <t>-58,65; 405,47</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,11; 35,85</t>
+          <t>-79,25; 35,17</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-64,94; 696,05</t>
+          <t>-67,98; 822,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-85,17; 458,05</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 5,85</t>
+          <t>-5,89; 6,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-7,83; 5,15</t>
+          <t>-8,37; 5,43</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 1,13</t>
+          <t>-7,29; 0,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,86; 0,44</t>
+          <t>-11,57; 0,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-61,06; 167,07</t>
+          <t>-64,78; 183,96</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-62,6; 92,29</t>
+          <t>-64,07; 87,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-93,22; 86,3</t>
+          <t>-91,59; 43,99</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 34,57</t>
+          <t>-100,0; 61,4</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,14; 2,8</t>
+          <t>-9,29; 3,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,52; 6,91</t>
+          <t>-5,73; 6,72</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,66; -1,64</t>
+          <t>-12,82; -1,95</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-13,13; 1,23</t>
+          <t>-11,29; 1,36</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-77,98; 69,56</t>
+          <t>-78,71; 73,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-58,16; 193,46</t>
+          <t>-59,09; 175,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 27,74</t>
+          <t>-100,0; 7,9</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 3,03</t>
+          <t>-4,87; 3,5</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 1,21</t>
+          <t>-7,52; 1,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,71; 0,94</t>
+          <t>-5,69; 1,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,21; 1,84</t>
+          <t>-4,23; 1,93</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,02; 67,02</t>
+          <t>-51,78; 76,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-58,74; 15,98</t>
+          <t>-57,35; 22,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-70,93; 27,67</t>
+          <t>-71,47; 33,08</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,77; 116,43</t>
+          <t>-76,12; 139,63</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,23; -1,45</t>
+          <t>-11,35; -1,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,1; 4,62</t>
+          <t>-6,53; 4,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 3,13</t>
+          <t>-5,99; 2,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 3,79</t>
+          <t>-1,03; 4,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-92,27; -12,35</t>
+          <t>-92,24; -14,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,74; 76,55</t>
+          <t>-53,43; 79,66</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,87; 89,12</t>
+          <t>-68,4; 87,04</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,51; 1316,73</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 6,85</t>
+          <t>-1,64; 6,66</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-15,34; -0,99</t>
+          <t>-16,55; -1,31</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,43; -1,96</t>
+          <t>-14,36; -2,21</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 7,74</t>
+          <t>-0,26; 7,11</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,97; 3,74</t>
+          <t>-100,0; 7,64</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 53,4</t>
+          <t>-100,0; 95,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,4; 0,83</t>
+          <t>-3,6; 0,75</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,12; 0,02</t>
+          <t>-5,0; -0,31</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,17; -0,54</t>
+          <t>-4,28; -0,71</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 0,97</t>
+          <t>-2,15; 0,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,35; 15,66</t>
+          <t>-46,92; 13,86</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,6; 0,69</t>
+          <t>-44,04; -1,91</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-62,27; -11,23</t>
+          <t>-62,11; -12,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-54,14; 42,95</t>
+          <t>-53,36; 46,52</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Clase-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 6,29</t>
+          <t>-3,38; 6,38</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 0,77</t>
+          <t>-10,63; 1,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 7,75</t>
+          <t>-1,62; 7,75</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,75</t>
+          <t>-3,04; 4,53</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-58,65; 405,47</t>
+          <t>-57,4; 310,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-79,25; 35,17</t>
+          <t>-80,84; 40,09</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-67,98; 822,63</t>
+          <t>-60,01; 724,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-85,17; 458,05</t>
+          <t>-79,49; 428,16</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 6,08</t>
+          <t>-5,74; 6,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,37; 5,43</t>
+          <t>-8,62; 4,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,29; 0,44</t>
+          <t>-7,24; 0,4</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-11,57; 0,43</t>
+          <t>-12,06; 0,25</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-64,78; 183,96</t>
+          <t>-63,21; 194,31</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-64,07; 87,78</t>
+          <t>-66,99; 77,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,59; 43,99</t>
+          <t>-91,79; 53,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 61,4</t>
+          <t>-100,0; 33,07</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-9,29; 3,53</t>
+          <t>-8,94; 3,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,73; 6,72</t>
+          <t>-6,87; 6,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,82; -1,95</t>
+          <t>-12,81; -1,73</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-11,29; 1,36</t>
+          <t>-12,17; 1,11</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,71; 73,63</t>
+          <t>-78,33; 73,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-59,09; 175,58</t>
+          <t>-65,81; 160,98</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,9</t>
+          <t>-100,0; 29,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>-0,85</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-26,02%</t>
+          <t>-25,74%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 3,5</t>
+          <t>-4,95; 3,25</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,52; 1,76</t>
+          <t>-7,21; 1,92</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,69; 1,04</t>
+          <t>-5,6; 1,08</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,23; 1,93</t>
+          <t>-3,99; 1,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-51,78; 76,99</t>
+          <t>-54,35; 74,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,35; 22,77</t>
+          <t>-57,58; 23,29</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,47; 33,08</t>
+          <t>-71,82; 36,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,12; 139,63</t>
+          <t>-76,83; 132,18</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,35; -1,86</t>
+          <t>-10,72; -1,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,53; 4,81</t>
+          <t>-6,57; 4,75</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-5,99; 2,86</t>
+          <t>-6,17; 2,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 4,02</t>
+          <t>-1,17; 4,09</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-92,24; -14,4</t>
+          <t>-92,16; -12,25</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-53,43; 79,66</t>
+          <t>-51,82; 74,57</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-68,4; 87,04</t>
+          <t>-71,31; 90,58</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-82,61; —</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,64; 6,66</t>
+          <t>-1,68; 7,11</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,55; -1,31</t>
+          <t>-16,56; -1,54</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,36; -2,21</t>
+          <t>-14,13; -2,11</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 7,11</t>
+          <t>-0,22; 7,42</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 7,64</t>
+          <t>-91,76; 6,01</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 95,18</t>
+          <t>-100,0; 11,26</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-18,83%</t>
+          <t>-18,73%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,6; 0,75</t>
+          <t>-3,31; 0,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,0; -0,31</t>
+          <t>-5,27; -0,28</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,28; -0,71</t>
+          <t>-4,13; -0,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 0,99</t>
+          <t>-2,05; 0,93</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,92; 13,86</t>
+          <t>-43,82; 12,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-44,04; -1,91</t>
+          <t>-46,52; -1,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-62,11; -12,53</t>
+          <t>-61,92; -12,53</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-53,36; 46,52</t>
+          <t>-51,42; 42,34</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Clase-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,71</t>
+          <t>0,65</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>23,57%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 6,38</t>
+          <t>-3,14; 6,27</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,63; 1,59</t>
+          <t>-11,08; 1,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 7,75</t>
+          <t>-2,04; 8,23</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 4,53</t>
+          <t>-2,9; 4,58</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-57,4; 310,41</t>
+          <t>-53,55; 329,74</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-80,84; 40,09</t>
+          <t>-80,11; 35,85</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-60,01; 724,84</t>
+          <t>-64,94; 696,05</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-79,49; 428,16</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-4,87</t>
+          <t>-4,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>-64,55%</t>
+          <t>-63,8%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,74; 6,35</t>
+          <t>-5,69; 5,85</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,62; 4,73</t>
+          <t>-7,83; 5,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-7,24; 0,4</t>
+          <t>-7,31; 1,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-12,06; 0,25</t>
+          <t>-11,48; 0,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-63,21; 194,31</t>
+          <t>-61,06; 167,07</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-66,99; 77,88</t>
+          <t>-62,6; 92,29</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-91,79; 53,8</t>
+          <t>-93,22; 86,3</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 33,07</t>
+          <t>-100,0; 39,24</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-4,31</t>
+          <t>-4,8</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-75,27%</t>
+          <t>-77,03%</t>
         </is>
       </c>
     </row>
@@ -860,37 +860,37 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,94; 3,79</t>
+          <t>-9,14; 2,8</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 6,12</t>
+          <t>-5,52; 6,91</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -1,73</t>
+          <t>-12,66; -1,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-12,17; 1,11</t>
+          <t>-13,98; 0,9</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-78,33; 73,69</t>
+          <t>-77,98; 69,56</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-65,81; 160,98</t>
+          <t>-58,16; 193,46</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 29,0</t>
+          <t>-100,0; 27,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>-0,85</t>
+          <t>-0,26</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>-25,74%</t>
+          <t>-8,29%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,95; 3,25</t>
+          <t>-4,76; 3,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-7,21; 1,92</t>
+          <t>-7,6; 1,21</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-5,6; 1,08</t>
+          <t>-5,71; 0,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 1,98</t>
+          <t>-3,18; 2,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-54,35; 74,23</t>
+          <t>-51,02; 67,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-57,58; 23,29</t>
+          <t>-58,74; 15,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-71,82; 36,15</t>
+          <t>-70,93; 27,67</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-76,83; 132,18</t>
+          <t>-70,19; 176,91</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,12</t>
+          <t>0,98</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>81,19%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,72; -1,35</t>
+          <t>-10,23; -1,45</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-6,57; 4,75</t>
+          <t>-6,1; 4,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-6,17; 2,82</t>
+          <t>-6,0; 3,13</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 4,09</t>
+          <t>-1,44; 3,71</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-92,16; -12,25</t>
+          <t>-92,27; -12,35</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-51,82; 74,57</t>
+          <t>-51,74; 76,55</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-71,31; 90,58</t>
+          <t>-68,87; 89,12</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-82,61; —</t>
+          <t>-87,22; 1170,78</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>2,69</t>
+          <t>3,0</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>352,05%</t>
+          <t>449,51%</t>
         </is>
       </c>
     </row>
@@ -1160,22 +1160,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 7,11</t>
+          <t>-1,65; 6,85</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-16,56; -1,54</t>
+          <t>-15,34; -0,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-14,13; -2,11</t>
+          <t>-13,43; -1,96</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 7,42</t>
+          <t>0,0; 8,43</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-91,76; 6,01</t>
+          <t>-91,97; 3,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 11,26</t>
+          <t>-100,0; 53,4</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,6</t>
+          <t>-0,46</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-18,73%</t>
+          <t>-14,32%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,31; 0,73</t>
+          <t>-3,4; 0,83</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-5,27; -0,28</t>
+          <t>-5,12; 0,02</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; -0,6</t>
+          <t>-4,17; -0,54</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 0,93</t>
+          <t>-2,21; 1,23</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-43,82; 12,66</t>
+          <t>-44,35; 15,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-46,52; -1,85</t>
+          <t>-44,6; 0,69</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-61,92; -12,53</t>
+          <t>-62,27; -11,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-51,42; 42,34</t>
+          <t>-50,97; 58,51</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP11-Clase-trans_bre.xlsx
+++ b/data/trans_bre/IP11-Clase-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J18"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-4,75</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,65</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>38,25%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-47,74%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>82,56%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>23,57%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>1.552792542755225</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-4.747045214934742</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>2.287000814239542</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>0.6452128515630481</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.3825056790319329</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.4774304995540958</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.8256388938772126</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>0.235692912087943</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-3,14; 6,27</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-11,08; 1,7</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-2,04; 8,23</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-2,9; 4,58</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-53,55; 329,74</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-80,11; 35,85</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-64,94; 696,05</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-3.142297780414231</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-11.08442919332746</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-2.039706366897803</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-2.89784658429915</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.5355129846811703</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.801119028659142</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.6494178917380156</v>
+      </c>
+      <c r="J5" s="6" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>6.267499090211598</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>1.701246638821288</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.228632482320492</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.582571186153543</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>3.297419854285458</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.3584834213510584</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>6.960477267153268</v>
+      </c>
+      <c r="J6" s="6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>Grupo III</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>0,36</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-1,56</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-3,28</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-4,69</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,56%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-15,86%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>-62,7%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>-63,8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-5,69; 5,85</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-7,83; 5,15</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-7,31; 1,13</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-11,48; 0,52</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-61,06; 167,07</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-62,6; 92,29</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-93,22; 86,3</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 39,24</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>0.3639180673246978</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-1.557354703252603</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>-3.283057648794347</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>-4.689833701831922</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>0.05559189889224544</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.1586260516161127</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>-0.6270035365339964</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>-0.6380159185182325</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>Grupo IV y V</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>-3,07</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0,24</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-6,42</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-4,8</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-35,37%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>3,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>-85,08%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-77,03%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-5.690466594065435</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-7.83360025040338</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-7.309448246994569</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-11.48185048139155</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.6105992933923541</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.6260444301943081</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.9321930396941123</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-9,14; 2,8</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,52; 6,91</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-12,66; -1,64</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-13,98; 0,9</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-77,98; 69,56</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-58,16; 193,46</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 27,74</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>5.853482374716092</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>5.151534662991578</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>1.128146499305896</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>0.5192582544437249</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>1.670690867960274</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.9229108371196643</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.86300695985559</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.3924405475898633</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>Grupo VI</t>
+          <t>Grupo IV y V</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,299 +815,195 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-0,86</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-2,23</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-0,26</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-11,92%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-28,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-38,11%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,29%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>-3.067715637964451</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>0.2424524907923262</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>-6.416183275554414</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-4.802820031059284</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>-0.3536884886368105</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.03468298906515731</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>-0.8508364235828637</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.7703222061958882</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-4,76; 3,03</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-7,6; 1,21</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-5,71; 0,94</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-3,18; 2,69</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-51,02; 67,02</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-58,74; 15,98</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-70,93; 27,67</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-70,19; 176,91</t>
-        </is>
-      </c>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-9.142322429408438</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.523029717201744</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-12.65988036399101</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-13.98325817038443</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.7797537275025589</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.5815501027356322</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>Grupo VII</t>
-        </is>
-      </c>
+      <c r="A12" s="1" t="n"/>
       <c r="B12" s="3" t="inlineStr">
         <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>2.796351142559828</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>6.905184723507555</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>-1.644604816940289</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>0.9034283339170099</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6955877720032447</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>1.934582203286787</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.277398771457997</v>
+      </c>
+      <c r="J12" s="6" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-6,05</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,71</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-1,34</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,98</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-68,8%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-7,38%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>-21,63%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>81,19%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-10,23; -1,45</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-6,1; 4,62</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-6,0; 3,13</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-1,44; 3,71</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-92,27; -12,35</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-51,74; 76,55</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-68,87; 89,12</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-87,22; 1170,78</t>
-        </is>
+      <c r="C13" s="5" t="n">
+        <v>-0.8573230344813874</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>-3.005174341532894</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-2.228765860223596</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-0.2636114756093932</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1192041972201086</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>-0.2805200802047662</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.3810705363867382</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08290606118965455</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>No ha trabajado</t>
-        </is>
-      </c>
+      <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>2,09</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-8,68</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-6,83</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>3,0</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>122,04%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>-69,6%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-87,94%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>449,51%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-4.759133086741389</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-7.603697166927195</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-5.712496095636451</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-3.179582950039794</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.5102006646968764</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.5873712794209561</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.7093164564920607</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.7018725411552829</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>-1,65; 6,85</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>-15,34; -0,99</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>-13,43; -1,96</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 8,43</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>-91,97; 3,74</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 53,4</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3.032160902764492</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>1.213608248816388</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>0.9368396672491125</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>2.694239341318969</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.6701625637567316</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.1597717260190918</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.2767375801504983</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>1.769120824317502</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Total</t>
+          <t>Grupo VII</t>
         </is>
       </c>
       <c r="B16" s="3" t="inlineStr">
@@ -1210,97 +1011,289 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>-1,26</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-2,67</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-2,44</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>-0,46</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>-19,12%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-26,64%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-42,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-14,32%</t>
-        </is>
+      <c r="C16" s="5" t="n">
+        <v>-6.048051976660079</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.707910726943814</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>-1.335732334963197</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>0.9762326962141422</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.6879741589842762</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.07376010350773822</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>-0.216331960648167</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>0.8118777358494377</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n"/>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>-3,4; 0,83</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>-5,12; 0,02</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>-4,17; -0,54</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>-2,21; 1,23</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>-44,35; 15,66</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>-44,6; 0,69</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>-62,27; -11,23</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>-50,97; 58,51</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-10.22543459991221</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-6.104778032147685</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-5.997043308519904</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-1.435885143782203</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.9227289806627957</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.5173663102021572</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.6887056088816208</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.8721800897373461</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>-1.445905965234098</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>4.622459939138643</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>3.128525413297129</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.706329468593471</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>-0.1235407781262551</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.7655260696322868</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.8912009388573321</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>11.70776774243487</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>2.085016801570128</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>-8.676074347962107</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>-6.834903254205961</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>2.996321585444648</v>
+      </c>
+      <c r="G19" s="6" t="n">
+        <v>1.220376819607722</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>-0.6959847441681596</v>
+      </c>
+      <c r="I19" s="6" t="n">
+        <v>-0.8794021560602798</v>
+      </c>
+      <c r="J19" s="6" t="n">
+        <v>4.495104188979338</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>-1.654203769656452</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>-15.34172516423878</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>-13.42802481009132</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="6" t="inlineStr"/>
+      <c r="H20" s="6" t="n">
+        <v>-0.9196616739391745</v>
+      </c>
+      <c r="I20" s="6" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J20" s="6" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>6.848002465345878</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-0.9864023879896741</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-1.961731694772392</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>8.426844011941448</v>
+      </c>
+      <c r="G21" s="6" t="inlineStr"/>
+      <c r="H21" s="6" t="n">
+        <v>0.03744160389708017</v>
+      </c>
+      <c r="I21" s="6" t="n">
+        <v>0.5339660067072306</v>
+      </c>
+      <c r="J21" s="6" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>-1.261666220711296</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>-2.665520527815528</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>-2.442856531635599</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>-0.4629209970450968</v>
+      </c>
+      <c r="G22" s="6" t="n">
+        <v>-0.1912475879925904</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>-0.2664372109047162</v>
+      </c>
+      <c r="I22" s="6" t="n">
+        <v>-0.4249339888128339</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>-0.1432155753077956</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="n">
+        <v>-3.399099575867449</v>
+      </c>
+      <c r="D23" s="5" t="n">
+        <v>-5.122794088179273</v>
+      </c>
+      <c r="E23" s="5" t="n">
+        <v>-4.167491054572912</v>
+      </c>
+      <c r="F23" s="5" t="n">
+        <v>-2.206998301591738</v>
+      </c>
+      <c r="G23" s="6" t="n">
+        <v>-0.4434680402992984</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>-0.4460369186661498</v>
+      </c>
+      <c r="I23" s="6" t="n">
+        <v>-0.6227119719530525</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>-0.509723910275249</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>0.8349818963980534</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>0.02362377616271523</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>-0.5381844741012195</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1.230895009969084</v>
+      </c>
+      <c r="G24" s="6" t="n">
+        <v>0.1565705074052863</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>0.006943774319505716</v>
+      </c>
+      <c r="I24" s="6" t="n">
+        <v>-0.1122762797208716</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.5850999742374239</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1308,16 +1301,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
     <mergeCell ref="A1:B2"/>
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="A16:A17"/>
-    <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
-    <mergeCell ref="A14:A15"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
